--- a/Fortran/results/Test_results.xlsx
+++ b/Fortran/results/Test_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\proek\Documents\GitHub\ModAB-Root-Finding\Fortran\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F88AAD-A1BD-451F-819F-ACC799478223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB157BDB-724B-42B6-B7D7-2DD50D4E3297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{901E7075-F730-4135-A5B3-71A5C4E5AAAF}"/>
   </bookViews>
@@ -9469,13 +9469,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9487,25 +9487,10 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9520,10 +9505,25 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9531,34 +9531,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8D166447-D689-4ADE-8B9D-041E58ED6DF7}"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <u/>
-      </font>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -11793,7 +11766,7 @@
       <c r="A4" s="14">
         <v>2</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="66" t="s">
         <v>245</v>
       </c>
       <c r="C4" s="53"/>
@@ -12036,7 +12009,7 @@
       <c r="A5" s="14">
         <v>3</v>
       </c>
-      <c r="B5" s="51"/>
+      <c r="B5" s="67"/>
       <c r="C5" s="54"/>
       <c r="D5" s="27" t="s">
         <v>67</v>
@@ -12277,7 +12250,7 @@
       <c r="A6" s="14">
         <v>4</v>
       </c>
-      <c r="B6" s="51"/>
+      <c r="B6" s="67"/>
       <c r="C6" s="54"/>
       <c r="D6" s="27" t="s">
         <v>68</v>
@@ -12518,7 +12491,7 @@
       <c r="A7" s="14">
         <v>5</v>
       </c>
-      <c r="B7" s="51"/>
+      <c r="B7" s="67"/>
       <c r="C7" s="54"/>
       <c r="D7" s="27" t="s">
         <v>69</v>
@@ -12759,7 +12732,7 @@
       <c r="A8" s="14">
         <v>6</v>
       </c>
-      <c r="B8" s="51"/>
+      <c r="B8" s="67"/>
       <c r="C8" s="54"/>
       <c r="D8" s="27" t="s">
         <v>75</v>
@@ -13000,7 +12973,7 @@
       <c r="A9" s="14">
         <v>7</v>
       </c>
-      <c r="B9" s="51"/>
+      <c r="B9" s="67"/>
       <c r="C9" s="54"/>
       <c r="D9" s="27" t="s">
         <v>74</v>
@@ -13241,7 +13214,7 @@
       <c r="A10" s="14">
         <v>8</v>
       </c>
-      <c r="B10" s="51"/>
+      <c r="B10" s="67"/>
       <c r="C10" s="54"/>
       <c r="D10" s="27" t="s">
         <v>73</v>
@@ -13482,7 +13455,7 @@
       <c r="A11" s="14">
         <v>9</v>
       </c>
-      <c r="B11" s="51"/>
+      <c r="B11" s="67"/>
       <c r="C11" s="54"/>
       <c r="D11" s="27" t="s">
         <v>72</v>
@@ -13723,7 +13696,7 @@
       <c r="A12" s="14">
         <v>10</v>
       </c>
-      <c r="B12" s="51"/>
+      <c r="B12" s="67"/>
       <c r="C12" s="54"/>
       <c r="D12" s="27" t="s">
         <v>71</v>
@@ -13964,7 +13937,7 @@
       <c r="A13" s="14">
         <v>11</v>
       </c>
-      <c r="B13" s="52"/>
+      <c r="B13" s="68"/>
       <c r="C13" s="55"/>
       <c r="D13" s="27" t="s">
         <v>70</v>
@@ -14205,7 +14178,7 @@
       <c r="A14" s="14">
         <v>12</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="66" t="s">
         <v>214</v>
       </c>
       <c r="C14" s="26">
@@ -14450,7 +14423,7 @@
       <c r="A15" s="14">
         <v>12</v>
       </c>
-      <c r="B15" s="51"/>
+      <c r="B15" s="67"/>
       <c r="C15" s="26">
         <v>100</v>
       </c>
@@ -14693,7 +14666,7 @@
       <c r="A16" s="14">
         <v>12</v>
       </c>
-      <c r="B16" s="52"/>
+      <c r="B16" s="68"/>
       <c r="C16" s="26">
         <v>200</v>
       </c>
@@ -15422,7 +15395,7 @@
       <c r="A19" s="14">
         <v>15</v>
       </c>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="50" t="s">
         <v>63</v>
       </c>
       <c r="C19" s="26">
@@ -15667,7 +15640,7 @@
       <c r="A20" s="14">
         <v>15</v>
       </c>
-      <c r="B20" s="57"/>
+      <c r="B20" s="51"/>
       <c r="C20" s="26">
         <v>6</v>
       </c>
@@ -15910,7 +15883,7 @@
       <c r="A21" s="14">
         <v>15</v>
       </c>
-      <c r="B21" s="57"/>
+      <c r="B21" s="51"/>
       <c r="C21" s="26">
         <v>8</v>
       </c>
@@ -16153,7 +16126,7 @@
       <c r="A22" s="14">
         <v>15</v>
       </c>
-      <c r="B22" s="57"/>
+      <c r="B22" s="51"/>
       <c r="C22" s="26">
         <v>10</v>
       </c>
@@ -16396,7 +16369,7 @@
       <c r="A23" s="14">
         <v>15</v>
       </c>
-      <c r="B23" s="58"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="26">
         <v>12</v>
       </c>
@@ -16639,7 +16612,7 @@
       <c r="A24" s="14">
         <v>16</v>
       </c>
-      <c r="B24" s="56" t="s">
+      <c r="B24" s="50" t="s">
         <v>62</v>
       </c>
       <c r="C24" s="26">
@@ -16884,7 +16857,7 @@
       <c r="A25" s="14">
         <v>16</v>
       </c>
-      <c r="B25" s="57"/>
+      <c r="B25" s="51"/>
       <c r="C25" s="26">
         <v>6</v>
       </c>
@@ -17127,7 +17100,7 @@
       <c r="A26" s="14">
         <v>16</v>
       </c>
-      <c r="B26" s="57"/>
+      <c r="B26" s="51"/>
       <c r="C26" s="26">
         <v>8</v>
       </c>
@@ -17370,7 +17343,7 @@
       <c r="A27" s="14">
         <v>16</v>
       </c>
-      <c r="B27" s="57"/>
+      <c r="B27" s="51"/>
       <c r="C27" s="26">
         <v>10</v>
       </c>
@@ -17613,7 +17586,7 @@
       <c r="A28" s="14">
         <v>16</v>
       </c>
-      <c r="B28" s="58"/>
+      <c r="B28" s="52"/>
       <c r="C28" s="26">
         <v>12</v>
       </c>
@@ -17856,7 +17829,7 @@
       <c r="A29" s="14">
         <v>17</v>
       </c>
-      <c r="B29" s="56" t="s">
+      <c r="B29" s="50" t="s">
         <v>62</v>
       </c>
       <c r="C29" s="26">
@@ -18101,7 +18074,7 @@
       <c r="A30" s="14">
         <v>17</v>
       </c>
-      <c r="B30" s="57"/>
+      <c r="B30" s="51"/>
       <c r="C30" s="26">
         <v>10</v>
       </c>
@@ -18344,7 +18317,7 @@
       <c r="A31" s="14">
         <v>17</v>
       </c>
-      <c r="B31" s="57"/>
+      <c r="B31" s="51"/>
       <c r="C31" s="26">
         <v>12</v>
       </c>
@@ -18587,7 +18560,7 @@
       <c r="A32" s="14">
         <v>17</v>
       </c>
-      <c r="B32" s="58"/>
+      <c r="B32" s="52"/>
       <c r="C32" s="26">
         <v>14</v>
       </c>
@@ -19073,7 +19046,7 @@
       <c r="A34" s="14">
         <v>19</v>
       </c>
-      <c r="B34" s="56" t="s">
+      <c r="B34" s="50" t="s">
         <v>269</v>
       </c>
       <c r="C34" s="26">
@@ -19318,7 +19291,7 @@
       <c r="A35" s="14">
         <v>19</v>
       </c>
-      <c r="B35" s="57"/>
+      <c r="B35" s="51"/>
       <c r="C35" s="26">
         <v>2</v>
       </c>
@@ -19561,7 +19534,7 @@
       <c r="A36" s="14">
         <v>19</v>
       </c>
-      <c r="B36" s="57"/>
+      <c r="B36" s="51"/>
       <c r="C36" s="26">
         <v>3</v>
       </c>
@@ -19804,7 +19777,7 @@
       <c r="A37" s="14">
         <v>19</v>
       </c>
-      <c r="B37" s="57"/>
+      <c r="B37" s="51"/>
       <c r="C37" s="26">
         <v>4</v>
       </c>
@@ -20047,7 +20020,7 @@
       <c r="A38" s="14">
         <v>19</v>
       </c>
-      <c r="B38" s="57"/>
+      <c r="B38" s="51"/>
       <c r="C38" s="26">
         <v>5</v>
       </c>
@@ -20290,7 +20263,7 @@
       <c r="A39" s="14">
         <v>19</v>
       </c>
-      <c r="B39" s="57"/>
+      <c r="B39" s="51"/>
       <c r="C39" s="26">
         <v>10</v>
       </c>
@@ -20533,7 +20506,7 @@
       <c r="A40" s="14">
         <v>19</v>
       </c>
-      <c r="B40" s="57"/>
+      <c r="B40" s="51"/>
       <c r="C40" s="26">
         <v>20</v>
       </c>
@@ -20776,7 +20749,7 @@
       <c r="A41" s="14">
         <v>19</v>
       </c>
-      <c r="B41" s="57"/>
+      <c r="B41" s="51"/>
       <c r="C41" s="26">
         <v>40</v>
       </c>
@@ -21019,7 +20992,7 @@
       <c r="A42" s="14">
         <v>19</v>
       </c>
-      <c r="B42" s="57"/>
+      <c r="B42" s="51"/>
       <c r="C42" s="26">
         <v>60</v>
       </c>
@@ -21262,7 +21235,7 @@
       <c r="A43" s="14">
         <v>19</v>
       </c>
-      <c r="B43" s="57"/>
+      <c r="B43" s="51"/>
       <c r="C43" s="26">
         <v>80</v>
       </c>
@@ -21505,7 +21478,7 @@
       <c r="A44" s="14">
         <v>19</v>
       </c>
-      <c r="B44" s="58"/>
+      <c r="B44" s="52"/>
       <c r="C44" s="26">
         <v>100</v>
       </c>
@@ -21748,7 +21721,7 @@
       <c r="A45" s="14">
         <v>20</v>
       </c>
-      <c r="B45" s="56" t="s">
+      <c r="B45" s="50" t="s">
         <v>268</v>
       </c>
       <c r="C45" s="26">
@@ -21993,7 +21966,7 @@
       <c r="A46" s="14">
         <v>20</v>
       </c>
-      <c r="B46" s="57"/>
+      <c r="B46" s="51"/>
       <c r="C46" s="26">
         <v>10</v>
       </c>
@@ -22236,7 +22209,7 @@
       <c r="A47" s="14">
         <v>20</v>
       </c>
-      <c r="B47" s="58"/>
+      <c r="B47" s="52"/>
       <c r="C47" s="26">
         <v>20</v>
       </c>
@@ -22479,7 +22452,7 @@
       <c r="A48" s="14">
         <v>21</v>
       </c>
-      <c r="B48" s="56" t="s">
+      <c r="B48" s="50" t="s">
         <v>64</v>
       </c>
       <c r="C48" s="26">
@@ -22724,7 +22697,7 @@
       <c r="A49" s="14">
         <v>21</v>
       </c>
-      <c r="B49" s="57"/>
+      <c r="B49" s="51"/>
       <c r="C49" s="26">
         <v>5</v>
       </c>
@@ -22967,7 +22940,7 @@
       <c r="A50" s="14">
         <v>21</v>
       </c>
-      <c r="B50" s="57"/>
+      <c r="B50" s="51"/>
       <c r="C50" s="26">
         <v>10</v>
       </c>
@@ -23210,7 +23183,7 @@
       <c r="A51" s="14">
         <v>21</v>
       </c>
-      <c r="B51" s="57"/>
+      <c r="B51" s="51"/>
       <c r="C51" s="26">
         <v>15</v>
       </c>
@@ -23453,7 +23426,7 @@
       <c r="A52" s="14">
         <v>21</v>
       </c>
-      <c r="B52" s="58"/>
+      <c r="B52" s="52"/>
       <c r="C52" s="26">
         <v>20</v>
       </c>
@@ -23696,7 +23669,7 @@
       <c r="A53" s="14">
         <v>22</v>
       </c>
-      <c r="B53" s="56" t="s">
+      <c r="B53" s="50" t="s">
         <v>211</v>
       </c>
       <c r="C53" s="26">
@@ -23941,7 +23914,7 @@
       <c r="A54" s="14">
         <v>22</v>
       </c>
-      <c r="B54" s="57"/>
+      <c r="B54" s="51"/>
       <c r="C54" s="26">
         <v>2</v>
       </c>
@@ -24184,7 +24157,7 @@
       <c r="A55" s="14">
         <v>22</v>
       </c>
-      <c r="B55" s="57"/>
+      <c r="B55" s="51"/>
       <c r="C55" s="26">
         <v>4</v>
       </c>
@@ -24427,7 +24400,7 @@
       <c r="A56" s="14">
         <v>22</v>
       </c>
-      <c r="B56" s="57"/>
+      <c r="B56" s="51"/>
       <c r="C56" s="26">
         <v>5</v>
       </c>
@@ -24670,7 +24643,7 @@
       <c r="A57" s="14">
         <v>22</v>
       </c>
-      <c r="B57" s="57"/>
+      <c r="B57" s="51"/>
       <c r="C57" s="26">
         <v>8</v>
       </c>
@@ -24913,7 +24886,7 @@
       <c r="A58" s="14">
         <v>22</v>
       </c>
-      <c r="B58" s="57"/>
+      <c r="B58" s="51"/>
       <c r="C58" s="26">
         <v>15</v>
       </c>
@@ -25156,7 +25129,7 @@
       <c r="A59" s="14">
         <v>22</v>
       </c>
-      <c r="B59" s="58"/>
+      <c r="B59" s="52"/>
       <c r="C59" s="26">
         <v>20</v>
       </c>
@@ -25399,7 +25372,7 @@
       <c r="A60" s="14">
         <v>23</v>
       </c>
-      <c r="B60" s="56" t="s">
+      <c r="B60" s="50" t="s">
         <v>180</v>
       </c>
       <c r="C60" s="26">
@@ -25644,7 +25617,7 @@
       <c r="A61" s="14">
         <v>23</v>
       </c>
-      <c r="B61" s="57"/>
+      <c r="B61" s="51"/>
       <c r="C61" s="26">
         <v>5</v>
       </c>
@@ -25887,7 +25860,7 @@
       <c r="A62" s="14">
         <v>23</v>
       </c>
-      <c r="B62" s="57"/>
+      <c r="B62" s="51"/>
       <c r="C62" s="26">
         <v>10</v>
       </c>
@@ -26130,7 +26103,7 @@
       <c r="A63" s="14">
         <v>23</v>
       </c>
-      <c r="B63" s="57"/>
+      <c r="B63" s="51"/>
       <c r="C63" s="26">
         <v>15</v>
       </c>
@@ -26373,7 +26346,7 @@
       <c r="A64" s="14">
         <v>23</v>
       </c>
-      <c r="B64" s="58"/>
+      <c r="B64" s="52"/>
       <c r="C64" s="26">
         <v>20</v>
       </c>
@@ -26616,7 +26589,7 @@
       <c r="A65" s="14">
         <v>24</v>
       </c>
-      <c r="B65" s="56" t="s">
+      <c r="B65" s="50" t="s">
         <v>210</v>
       </c>
       <c r="C65" s="26">
@@ -26861,7 +26834,7 @@
       <c r="A66" s="14">
         <v>24</v>
       </c>
-      <c r="B66" s="57"/>
+      <c r="B66" s="51"/>
       <c r="C66" s="26">
         <v>5</v>
       </c>
@@ -27104,7 +27077,7 @@
       <c r="A67" s="14">
         <v>24</v>
       </c>
-      <c r="B67" s="57"/>
+      <c r="B67" s="51"/>
       <c r="C67" s="26">
         <v>15</v>
       </c>
@@ -27347,7 +27320,7 @@
       <c r="A68" s="14">
         <v>24</v>
       </c>
-      <c r="B68" s="58"/>
+      <c r="B68" s="52"/>
       <c r="C68" s="26">
         <v>20</v>
       </c>
@@ -27590,7 +27563,7 @@
       <c r="A69" s="14">
         <v>25</v>
       </c>
-      <c r="B69" s="56" t="s">
+      <c r="B69" s="50" t="s">
         <v>216</v>
       </c>
       <c r="C69" s="26">
@@ -27835,7 +27808,7 @@
       <c r="A70" s="14">
         <v>25</v>
       </c>
-      <c r="B70" s="57"/>
+      <c r="B70" s="51"/>
       <c r="C70" s="26">
         <v>3</v>
       </c>
@@ -28078,7 +28051,7 @@
       <c r="A71" s="14">
         <v>25</v>
       </c>
-      <c r="B71" s="57"/>
+      <c r="B71" s="51"/>
       <c r="C71" s="26">
         <v>4</v>
       </c>
@@ -28321,7 +28294,7 @@
       <c r="A72" s="14">
         <v>25</v>
       </c>
-      <c r="B72" s="57"/>
+      <c r="B72" s="51"/>
       <c r="C72" s="26">
         <v>5</v>
       </c>
@@ -28564,7 +28537,7 @@
       <c r="A73" s="14">
         <v>25</v>
       </c>
-      <c r="B73" s="57"/>
+      <c r="B73" s="51"/>
       <c r="C73" s="26">
         <v>6</v>
       </c>
@@ -28807,7 +28780,7 @@
       <c r="A74" s="14">
         <v>25</v>
       </c>
-      <c r="B74" s="57"/>
+      <c r="B74" s="51"/>
       <c r="C74" s="26">
         <v>7</v>
       </c>
@@ -29050,7 +29023,7 @@
       <c r="A75" s="14">
         <v>25</v>
       </c>
-      <c r="B75" s="57"/>
+      <c r="B75" s="51"/>
       <c r="C75" s="26">
         <v>9</v>
       </c>
@@ -29293,7 +29266,7 @@
       <c r="A76" s="14">
         <v>25</v>
       </c>
-      <c r="B76" s="57"/>
+      <c r="B76" s="51"/>
       <c r="C76" s="26">
         <v>11</v>
       </c>
@@ -29536,7 +29509,7 @@
       <c r="A77" s="14">
         <v>25</v>
       </c>
-      <c r="B77" s="57"/>
+      <c r="B77" s="51"/>
       <c r="C77" s="26">
         <v>13</v>
       </c>
@@ -29779,7 +29752,7 @@
       <c r="A78" s="14">
         <v>25</v>
       </c>
-      <c r="B78" s="57"/>
+      <c r="B78" s="51"/>
       <c r="C78" s="26">
         <v>15</v>
       </c>
@@ -30022,7 +29995,7 @@
       <c r="A79" s="14">
         <v>25</v>
       </c>
-      <c r="B79" s="57"/>
+      <c r="B79" s="51"/>
       <c r="C79" s="26">
         <v>17</v>
       </c>
@@ -30265,7 +30238,7 @@
       <c r="A80" s="14">
         <v>25</v>
       </c>
-      <c r="B80" s="57"/>
+      <c r="B80" s="51"/>
       <c r="C80" s="26">
         <v>19</v>
       </c>
@@ -30508,7 +30481,7 @@
       <c r="A81" s="14">
         <v>25</v>
       </c>
-      <c r="B81" s="57"/>
+      <c r="B81" s="51"/>
       <c r="C81" s="26">
         <v>21</v>
       </c>
@@ -30751,7 +30724,7 @@
       <c r="A82" s="14">
         <v>25</v>
       </c>
-      <c r="B82" s="57"/>
+      <c r="B82" s="51"/>
       <c r="C82" s="26">
         <v>23</v>
       </c>
@@ -30994,7 +30967,7 @@
       <c r="A83" s="14">
         <v>25</v>
       </c>
-      <c r="B83" s="57"/>
+      <c r="B83" s="51"/>
       <c r="C83" s="26">
         <v>25</v>
       </c>
@@ -31237,7 +31210,7 @@
       <c r="A84" s="14">
         <v>25</v>
       </c>
-      <c r="B84" s="57"/>
+      <c r="B84" s="51"/>
       <c r="C84" s="26">
         <v>27</v>
       </c>
@@ -31480,7 +31453,7 @@
       <c r="A85" s="14">
         <v>25</v>
       </c>
-      <c r="B85" s="57"/>
+      <c r="B85" s="51"/>
       <c r="C85" s="26">
         <v>29</v>
       </c>
@@ -31723,7 +31696,7 @@
       <c r="A86" s="14">
         <v>25</v>
       </c>
-      <c r="B86" s="57"/>
+      <c r="B86" s="51"/>
       <c r="C86" s="26">
         <v>31</v>
       </c>
@@ -31966,7 +31939,7 @@
       <c r="A87" s="14">
         <v>25</v>
       </c>
-      <c r="B87" s="58"/>
+      <c r="B87" s="52"/>
       <c r="C87" s="26">
         <v>33</v>
       </c>
@@ -32274,7 +32247,7 @@
         <v>4</v>
       </c>
       <c r="X88" s="16">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y88" s="16">
         <v>8</v>
@@ -32517,7 +32490,7 @@
         <v>4</v>
       </c>
       <c r="X89" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y89" s="16">
         <v>8</v>
@@ -34429,7 +34402,7 @@
         <v>27</v>
       </c>
       <c r="J97" s="16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K97" s="16">
         <v>12</v>
@@ -34471,7 +34444,7 @@
         <v>11</v>
       </c>
       <c r="X97" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y97" s="16">
         <v>11</v>
@@ -35864,10 +35837,10 @@
       <c r="A103" s="14">
         <v>38</v>
       </c>
-      <c r="B103" s="61" t="s">
+      <c r="B103" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="C103" s="62"/>
+      <c r="C103" s="65"/>
       <c r="D103" s="26" t="s">
         <v>53</v>
       </c>
@@ -36107,10 +36080,10 @@
       <c r="A104" s="14">
         <v>39</v>
       </c>
-      <c r="B104" s="59" t="s">
+      <c r="B104" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="C104" s="60"/>
+      <c r="C104" s="63"/>
       <c r="D104" s="26" t="s">
         <v>53</v>
       </c>
@@ -38298,7 +38271,7 @@
       <c r="A113" s="14">
         <v>47</v>
       </c>
-      <c r="B113" s="56" t="s">
+      <c r="B113" s="50" t="s">
         <v>110</v>
       </c>
       <c r="C113" s="53"/>
@@ -38541,7 +38514,7 @@
       <c r="A114" s="14">
         <v>48</v>
       </c>
-      <c r="B114" s="58"/>
+      <c r="B114" s="52"/>
       <c r="C114" s="55"/>
       <c r="D114" s="26" t="s">
         <v>124</v>
@@ -38782,7 +38755,7 @@
       <c r="A115" s="14">
         <v>49</v>
       </c>
-      <c r="B115" s="56" t="s">
+      <c r="B115" s="50" t="s">
         <v>111</v>
       </c>
       <c r="C115" s="53"/>
@@ -39025,7 +38998,7 @@
       <c r="A116" s="14">
         <v>50</v>
       </c>
-      <c r="B116" s="58"/>
+      <c r="B116" s="52"/>
       <c r="C116" s="55"/>
       <c r="D116" s="26" t="s">
         <v>125</v>
@@ -39266,7 +39239,7 @@
       <c r="A117" s="14">
         <v>51</v>
       </c>
-      <c r="B117" s="56" t="s">
+      <c r="B117" s="50" t="s">
         <v>266</v>
       </c>
       <c r="C117" s="53"/>
@@ -39509,7 +39482,7 @@
       <c r="A118" s="14">
         <v>52</v>
       </c>
-      <c r="B118" s="58"/>
+      <c r="B118" s="52"/>
       <c r="C118" s="55"/>
       <c r="D118" s="26" t="s">
         <v>125</v>
@@ -39750,7 +39723,7 @@
       <c r="A119" s="14">
         <v>53</v>
       </c>
-      <c r="B119" s="56" t="s">
+      <c r="B119" s="50" t="s">
         <v>112</v>
       </c>
       <c r="C119" s="53"/>
@@ -39993,7 +39966,7 @@
       <c r="A120" s="14">
         <v>54</v>
       </c>
-      <c r="B120" s="58"/>
+      <c r="B120" s="52"/>
       <c r="C120" s="55"/>
       <c r="D120" s="26" t="s">
         <v>115</v>
@@ -40234,7 +40207,7 @@
       <c r="A121" s="14">
         <v>55</v>
       </c>
-      <c r="B121" s="56" t="s">
+      <c r="B121" s="50" t="s">
         <v>113</v>
       </c>
       <c r="C121" s="53"/>
@@ -40477,7 +40450,7 @@
       <c r="A122" s="14">
         <v>56</v>
       </c>
-      <c r="B122" s="58"/>
+      <c r="B122" s="52"/>
       <c r="C122" s="55"/>
       <c r="D122" s="26" t="s">
         <v>99</v>
@@ -40783,7 +40756,7 @@
         <v>4</v>
       </c>
       <c r="X123" s="16">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y123" s="16">
         <v>8</v>
@@ -41204,10 +41177,10 @@
       <c r="A125" s="14">
         <v>59</v>
       </c>
-      <c r="B125" s="65" t="s">
+      <c r="B125" s="60" t="s">
         <v>265</v>
       </c>
-      <c r="C125" s="66"/>
+      <c r="C125" s="61"/>
       <c r="D125" s="26" t="s">
         <v>160</v>
       </c>
@@ -41447,10 +41420,10 @@
       <c r="A126" s="14">
         <v>60</v>
       </c>
-      <c r="B126" s="63" t="s">
+      <c r="B126" s="58" t="s">
         <v>161</v>
       </c>
-      <c r="C126" s="64"/>
+      <c r="C126" s="59"/>
       <c r="D126" s="26" t="s">
         <v>158</v>
       </c>
@@ -41690,7 +41663,7 @@
       <c r="A127" s="14">
         <v>61</v>
       </c>
-      <c r="B127" s="56" t="s">
+      <c r="B127" s="50" t="s">
         <v>227</v>
       </c>
       <c r="C127" s="53"/>
@@ -41933,7 +41906,7 @@
       <c r="A128" s="14">
         <v>62</v>
       </c>
-      <c r="B128" s="58"/>
+      <c r="B128" s="52"/>
       <c r="C128" s="55"/>
       <c r="D128" s="26" t="s">
         <v>158</v>
@@ -42683,7 +42656,7 @@
         <v>32</v>
       </c>
       <c r="J131" s="16">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K131" s="16">
         <v>10</v>
@@ -44118,7 +44091,7 @@
       <c r="A137" s="14">
         <v>71</v>
       </c>
-      <c r="B137" s="67" t="s">
+      <c r="B137" s="56" t="s">
         <v>19</v>
       </c>
       <c r="C137" s="53"/>
@@ -44361,7 +44334,7 @@
       <c r="A138" s="14">
         <v>72</v>
       </c>
-      <c r="B138" s="68"/>
+      <c r="B138" s="57"/>
       <c r="C138" s="55"/>
       <c r="D138" s="26" t="s">
         <v>154</v>
@@ -45088,7 +45061,7 @@
       <c r="A141" s="14">
         <v>75</v>
       </c>
-      <c r="B141" s="56" t="s">
+      <c r="B141" s="50" t="s">
         <v>262</v>
       </c>
       <c r="C141" s="53"/>
@@ -45331,7 +45304,7 @@
       <c r="A142" s="14">
         <v>76</v>
       </c>
-      <c r="B142" s="57"/>
+      <c r="B142" s="51"/>
       <c r="C142" s="54"/>
       <c r="D142" s="26" t="s">
         <v>151</v>
@@ -45572,7 +45545,7 @@
       <c r="A143" s="14">
         <v>77</v>
       </c>
-      <c r="B143" s="57"/>
+      <c r="B143" s="51"/>
       <c r="C143" s="54"/>
       <c r="D143" s="26" t="s">
         <v>150</v>
@@ -45813,7 +45786,7 @@
       <c r="A144" s="14">
         <v>78</v>
       </c>
-      <c r="B144" s="58"/>
+      <c r="B144" s="52"/>
       <c r="C144" s="55"/>
       <c r="D144" s="26" t="s">
         <v>149</v>
@@ -46054,7 +46027,7 @@
       <c r="A145" s="14">
         <v>79</v>
       </c>
-      <c r="B145" s="56" t="s">
+      <c r="B145" s="50" t="s">
         <v>261</v>
       </c>
       <c r="C145" s="53"/>
@@ -46297,7 +46270,7 @@
       <c r="A146" s="14">
         <v>80</v>
       </c>
-      <c r="B146" s="57"/>
+      <c r="B146" s="51"/>
       <c r="C146" s="54"/>
       <c r="D146" s="26" t="s">
         <v>148</v>
@@ -46538,7 +46511,7 @@
       <c r="A147" s="14">
         <v>81</v>
       </c>
-      <c r="B147" s="57"/>
+      <c r="B147" s="51"/>
       <c r="C147" s="54"/>
       <c r="D147" s="26" t="s">
         <v>147</v>
@@ -46779,7 +46752,7 @@
       <c r="A148" s="14">
         <v>82</v>
       </c>
-      <c r="B148" s="58"/>
+      <c r="B148" s="52"/>
       <c r="C148" s="55"/>
       <c r="D148" s="26" t="s">
         <v>146</v>
@@ -47040,10 +47013,10 @@
         <v>22</v>
       </c>
       <c r="I149" s="16">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J149" s="16">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K149" s="16">
         <v>12</v>
@@ -47263,7 +47236,7 @@
       <c r="A150" s="14">
         <v>84</v>
       </c>
-      <c r="B150" s="56" t="s">
+      <c r="B150" s="50" t="s">
         <v>259</v>
       </c>
       <c r="C150" s="53"/>
@@ -47506,7 +47479,7 @@
       <c r="A151" s="14">
         <v>85</v>
       </c>
-      <c r="B151" s="58"/>
+      <c r="B151" s="52"/>
       <c r="C151" s="55"/>
       <c r="D151" s="26" t="s">
         <v>58</v>
@@ -47747,7 +47720,7 @@
       <c r="A152" s="14">
         <v>86</v>
       </c>
-      <c r="B152" s="56" t="s">
+      <c r="B152" s="50" t="s">
         <v>258</v>
       </c>
       <c r="C152" s="53"/>
@@ -47990,7 +47963,7 @@
       <c r="A153" s="14">
         <v>87</v>
       </c>
-      <c r="B153" s="57"/>
+      <c r="B153" s="51"/>
       <c r="C153" s="54"/>
       <c r="D153" s="26" t="s">
         <v>143</v>
@@ -48231,7 +48204,7 @@
       <c r="A154" s="14">
         <v>88</v>
       </c>
-      <c r="B154" s="58"/>
+      <c r="B154" s="52"/>
       <c r="C154" s="55"/>
       <c r="D154" s="26" t="s">
         <v>140</v>
@@ -48472,7 +48445,7 @@
       <c r="A155" s="14">
         <v>89</v>
       </c>
-      <c r="B155" s="56" t="s">
+      <c r="B155" s="50" t="s">
         <v>234</v>
       </c>
       <c r="C155" s="53"/>
@@ -48715,7 +48688,7 @@
       <c r="A156" s="14">
         <v>90</v>
       </c>
-      <c r="B156" s="58"/>
+      <c r="B156" s="52"/>
       <c r="C156" s="55"/>
       <c r="D156" s="26" t="s">
         <v>142</v>
@@ -49442,7 +49415,7 @@
       <c r="A159" s="14">
         <v>93</v>
       </c>
-      <c r="B159" s="56" t="s">
+      <c r="B159" s="50" t="s">
         <v>257</v>
       </c>
       <c r="C159" s="53"/>
@@ -49685,7 +49658,7 @@
       <c r="A160" s="14">
         <v>94</v>
       </c>
-      <c r="B160" s="58"/>
+      <c r="B160" s="52"/>
       <c r="C160" s="55"/>
       <c r="D160" s="26" t="s">
         <v>140</v>
@@ -49926,7 +49899,7 @@
       <c r="A161" s="14">
         <v>95</v>
       </c>
-      <c r="B161" s="56" t="s">
+      <c r="B161" s="50" t="s">
         <v>256</v>
       </c>
       <c r="C161" s="53"/>
@@ -50169,7 +50142,7 @@
       <c r="A162" s="14">
         <v>96</v>
       </c>
-      <c r="B162" s="57"/>
+      <c r="B162" s="51"/>
       <c r="C162" s="54"/>
       <c r="D162" s="26" t="s">
         <v>139</v>
@@ -50410,7 +50383,7 @@
       <c r="A163" s="14">
         <v>97</v>
       </c>
-      <c r="B163" s="57"/>
+      <c r="B163" s="51"/>
       <c r="C163" s="54"/>
       <c r="D163" s="26" t="s">
         <v>138</v>
@@ -50651,7 +50624,7 @@
       <c r="A164" s="14">
         <v>98</v>
       </c>
-      <c r="B164" s="58"/>
+      <c r="B164" s="52"/>
       <c r="C164" s="55"/>
       <c r="D164" s="26" t="s">
         <v>137</v>
@@ -51378,7 +51351,7 @@
       <c r="A167" s="14">
         <v>101</v>
       </c>
-      <c r="B167" s="56" t="s">
+      <c r="B167" s="50" t="s">
         <v>203</v>
       </c>
       <c r="C167" s="26">
@@ -51623,7 +51596,7 @@
       <c r="A168" s="14">
         <v>101</v>
       </c>
-      <c r="B168" s="57"/>
+      <c r="B168" s="51"/>
       <c r="C168" s="26">
         <v>10</v>
       </c>
@@ -51866,7 +51839,7 @@
       <c r="A169" s="14">
         <v>101</v>
       </c>
-      <c r="B169" s="58"/>
+      <c r="B169" s="52"/>
       <c r="C169" s="26">
         <v>20</v>
       </c>
@@ -56989,10 +56962,10 @@
         <v>22</v>
       </c>
       <c r="I190" s="16">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J190" s="16">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K190" s="16">
         <v>16</v>
@@ -60148,7 +60121,7 @@
         <v>30</v>
       </c>
       <c r="I203" s="16">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J203" s="16">
         <v>22</v>
@@ -60166,13 +60139,13 @@
         <v>12</v>
       </c>
       <c r="O203" s="16">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P203" s="16">
         <v>20</v>
       </c>
       <c r="Q203" s="16">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R203" s="16">
         <v>18</v>
@@ -64988,7 +64961,7 @@
       <c r="A223" s="14">
         <v>155</v>
       </c>
-      <c r="B223" s="56" t="s">
+      <c r="B223" s="50" t="s">
         <v>187</v>
       </c>
       <c r="C223" s="53"/>
@@ -65231,7 +65204,7 @@
       <c r="A224" s="14">
         <v>156</v>
       </c>
-      <c r="B224" s="57"/>
+      <c r="B224" s="51"/>
       <c r="C224" s="54"/>
       <c r="D224" s="26" t="s">
         <v>50</v>
@@ -65472,7 +65445,7 @@
       <c r="A225" s="14">
         <v>157</v>
       </c>
-      <c r="B225" s="58"/>
+      <c r="B225" s="52"/>
       <c r="C225" s="55"/>
       <c r="D225" s="26" t="s">
         <v>51</v>
@@ -65731,11 +65704,11 @@
       </c>
       <c r="I226" s="21">
         <f t="shared" si="170"/>
-        <v>8603</v>
+        <v>8605</v>
       </c>
       <c r="J226" s="21">
         <f t="shared" si="170"/>
-        <v>3887</v>
+        <v>3884</v>
       </c>
       <c r="K226" s="21">
         <f t="shared" si="170"/>
@@ -65755,7 +65728,7 @@
       </c>
       <c r="O226" s="21">
         <f t="shared" si="170"/>
-        <v>3501</v>
+        <v>3503</v>
       </c>
       <c r="P226" s="21">
         <f t="shared" si="170"/>
@@ -65763,7 +65736,7 @@
       </c>
       <c r="Q226" s="21">
         <f t="shared" si="170"/>
-        <v>5996</v>
+        <v>5995</v>
       </c>
       <c r="R226" s="21">
         <f t="shared" si="170"/>
@@ -65791,7 +65764,7 @@
       </c>
       <c r="X226" s="45">
         <f t="shared" si="170"/>
-        <v>2666</v>
+        <v>2661</v>
       </c>
       <c r="Y226" s="21">
         <f>SUM(Y3:Y225)</f>
@@ -65987,11 +65960,11 @@
       </c>
       <c r="I227" s="22">
         <f t="shared" si="191"/>
-        <v>38.578475336322867</v>
+        <v>38.587443946188344</v>
       </c>
       <c r="J227" s="22">
         <f t="shared" si="191"/>
-        <v>17.430493273542602</v>
+        <v>17.417040358744394</v>
       </c>
       <c r="K227" s="22">
         <f t="shared" si="191"/>
@@ -66011,7 +65984,7 @@
       </c>
       <c r="O227" s="22">
         <f t="shared" si="191"/>
-        <v>15.699551569506726</v>
+        <v>15.708520179372197</v>
       </c>
       <c r="P227" s="22">
         <f t="shared" si="191"/>
@@ -66019,7 +65992,7 @@
       </c>
       <c r="Q227" s="22">
         <f t="shared" si="191"/>
-        <v>26.887892376681613</v>
+        <v>26.883408071748878</v>
       </c>
       <c r="R227" s="22">
         <f t="shared" si="191"/>
@@ -66047,7 +66020,7 @@
       </c>
       <c r="X227" s="46">
         <f t="shared" si="191"/>
-        <v>11.955156950672645</v>
+        <v>11.932735426008968</v>
       </c>
       <c r="Y227" s="22">
         <f>AVERAGE(Y3:Y225)</f>
@@ -66333,11 +66306,11 @@
       </c>
       <c r="I229" s="22">
         <f t="shared" si="193"/>
-        <v>31.2021591012968</v>
+        <v>31.212455778601782</v>
       </c>
       <c r="J229" s="22">
         <f t="shared" si="193"/>
-        <v>15.796438790299655</v>
+        <v>15.78394425758273</v>
       </c>
       <c r="K229" s="22">
         <f t="shared" si="193"/>
@@ -66357,7 +66330,7 @@
       </c>
       <c r="O229" s="22">
         <f t="shared" si="193"/>
-        <v>13.736418935596493</v>
+        <v>13.742291134604821</v>
       </c>
       <c r="P229" s="22">
         <f t="shared" si="193"/>
@@ -66365,7 +66338,7 @@
       </c>
       <c r="Q229" s="22">
         <f t="shared" si="193"/>
-        <v>15.837101043583237</v>
+        <v>15.835207220844556</v>
       </c>
       <c r="R229" s="22">
         <f t="shared" si="193"/>
@@ -66393,7 +66366,7 @@
       </c>
       <c r="X229" s="46">
         <f t="shared" si="193"/>
-        <v>11.014667570795707</v>
+        <v>10.989820259734769</v>
       </c>
       <c r="Y229" s="22">
         <f t="shared" si="193"/>
@@ -66857,11 +66830,11 @@
       </c>
       <c r="I233" s="22">
         <f t="shared" si="197"/>
-        <v>39.596863596425649</v>
+        <v>39.594000640001035</v>
       </c>
       <c r="J233" s="22">
         <f t="shared" si="197"/>
-        <v>10.227738437179989</v>
+        <v>10.227637712739366</v>
       </c>
       <c r="K233" s="22">
         <f t="shared" si="197"/>
@@ -66881,7 +66854,7 @@
       </c>
       <c r="O233" s="22">
         <f t="shared" si="197"/>
-        <v>10.330761803354287</v>
+        <v>10.335379151955726</v>
       </c>
       <c r="P233" s="22">
         <f t="shared" si="197"/>
@@ -66889,7 +66862,7 @@
       </c>
       <c r="Q233" s="22">
         <f t="shared" si="197"/>
-        <v>37.005124876961787</v>
+        <v>37.003832806707756</v>
       </c>
       <c r="R233" s="22">
         <f t="shared" si="197"/>
@@ -66917,7 +66890,7 @@
       </c>
       <c r="X233" s="46">
         <f t="shared" si="197"/>
-        <v>6.3712302295096572</v>
+        <v>6.3784515586105339</v>
       </c>
       <c r="Y233" s="22">
         <f t="shared" si="197"/>
@@ -66988,11 +66961,11 @@
       </c>
       <c r="I234" s="24">
         <f t="shared" si="198"/>
-        <v>2.6516021104044007</v>
+        <v>2.651410392661933</v>
       </c>
       <c r="J234" s="24">
         <f t="shared" si="198"/>
-        <v>0.68490002392863103</v>
+        <v>0.68489327892119689</v>
       </c>
       <c r="K234" s="24">
         <f t="shared" si="198"/>
@@ -67012,7 +66985,7 @@
       </c>
       <c r="O234" s="24">
         <f t="shared" si="198"/>
-        <v>0.6917989788042741</v>
+        <v>0.69210817933643831</v>
       </c>
       <c r="P234" s="24">
         <f t="shared" si="198"/>
@@ -67020,7 +66993,7 @@
       </c>
       <c r="Q234" s="24">
         <f t="shared" si="198"/>
-        <v>2.478046448819943</v>
+        <v>2.4779599253960858</v>
       </c>
       <c r="R234" s="24">
         <f t="shared" si="198"/>
@@ -67048,7 +67021,7 @@
       </c>
       <c r="X234" s="48">
         <f t="shared" si="198"/>
-        <v>0.42664913298752061</v>
+        <v>0.42713270895149008</v>
       </c>
       <c r="Y234" s="24">
         <f t="shared" si="198"/>
@@ -67107,75 +67080,75 @@
       </c>
       <c r="F235" s="24">
         <f>F227/$X$227</f>
-        <v>3.7996999249812453</v>
+        <v>3.8068395340097707</v>
       </c>
       <c r="G235" s="24">
         <f t="shared" ref="G235:Y235" si="199">G227/$X$227</f>
-        <v>33.460990247561895</v>
+        <v>33.523863209319806</v>
       </c>
       <c r="H235" s="24">
         <f t="shared" si="199"/>
-        <v>1.9054763690922731</v>
+        <v>1.909056745584367</v>
       </c>
       <c r="I235" s="24">
         <f t="shared" si="199"/>
-        <v>3.2269317329332332</v>
+        <v>3.2337467117624956</v>
       </c>
       <c r="J235" s="24">
         <f t="shared" si="199"/>
-        <v>1.4579894973743437</v>
+        <v>1.4596016535137166</v>
       </c>
       <c r="K235" s="24">
         <f t="shared" si="199"/>
-        <v>1.3087021755438861</v>
+        <v>1.3111612175873733</v>
       </c>
       <c r="L235" s="24">
         <f t="shared" si="199"/>
-        <v>1.9951237809452365</v>
+        <v>1.9988726042841038</v>
       </c>
       <c r="M235" s="24">
         <f t="shared" si="199"/>
-        <v>2.3713428357089272</v>
+        <v>2.3757985719654267</v>
       </c>
       <c r="N235" s="24">
         <f t="shared" si="199"/>
-        <v>1.4722430607651915</v>
+        <v>1.4750093949642993</v>
       </c>
       <c r="O235" s="24">
         <f t="shared" si="199"/>
-        <v>1.3132033008252064</v>
+        <v>1.3164223975948892</v>
       </c>
       <c r="P235" s="24">
         <f t="shared" si="199"/>
-        <v>9.1069017254313582</v>
+        <v>9.1240135287485913</v>
       </c>
       <c r="Q235" s="24">
         <f t="shared" si="199"/>
-        <v>2.2490622655663914</v>
+        <v>2.2529124389327322</v>
       </c>
       <c r="R235" s="24">
         <f t="shared" si="199"/>
-        <v>1.3060765191297825</v>
+        <v>1.3085306275836153</v>
       </c>
       <c r="S235" s="24">
         <f t="shared" si="199"/>
-        <v>1.2111777944486122</v>
+        <v>1.2134535888763622</v>
       </c>
       <c r="T235" s="24">
         <f t="shared" si="199"/>
-        <v>1.2104276069017255</v>
+        <v>1.2127019917324315</v>
       </c>
       <c r="U235" s="24">
         <f t="shared" si="199"/>
-        <v>5.2393098274568644</v>
+        <v>5.2491544532130785</v>
       </c>
       <c r="V235" s="24">
         <f t="shared" si="199"/>
-        <v>1.187921980495124</v>
+        <v>1.1901540774145061</v>
       </c>
       <c r="W235" s="24">
         <f t="shared" si="199"/>
-        <v>1.6395348837209305</v>
+        <v>1.6426155580608797</v>
       </c>
       <c r="X235" s="48">
         <f t="shared" si="199"/>
@@ -67183,7 +67156,7 @@
       </c>
       <c r="Y235" s="24">
         <f t="shared" si="199"/>
-        <v>0.98799699924981255</v>
+        <v>0.98985343855693364</v>
       </c>
       <c r="Z235" s="37"/>
       <c r="AA235" s="37"/>
@@ -67341,20 +67314,27 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="B223:B225"/>
-    <mergeCell ref="C223:C225"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="B161:B164"/>
-    <mergeCell ref="C161:C164"/>
-    <mergeCell ref="B167:B169"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="C127:C128"/>
-    <mergeCell ref="B141:B144"/>
-    <mergeCell ref="C141:C144"/>
-    <mergeCell ref="B145:B148"/>
-    <mergeCell ref="C145:C148"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="B4:B13"/>
+    <mergeCell ref="C4:C13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="B69:B87"/>
+    <mergeCell ref="B34:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B52"/>
+    <mergeCell ref="B53:B59"/>
+    <mergeCell ref="B60:B64"/>
+    <mergeCell ref="B65:B68"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="C121:C122"/>
     <mergeCell ref="B159:B160"/>
     <mergeCell ref="C159:C160"/>
     <mergeCell ref="C117:C118"/>
@@ -67371,27 +67351,20 @@
     <mergeCell ref="B126:C126"/>
     <mergeCell ref="B125:C125"/>
     <mergeCell ref="B127:B128"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="B69:B87"/>
-    <mergeCell ref="B34:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B52"/>
-    <mergeCell ref="B53:B59"/>
-    <mergeCell ref="B60:B64"/>
-    <mergeCell ref="B65:B68"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="B4:B13"/>
-    <mergeCell ref="C4:C13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="B141:B144"/>
+    <mergeCell ref="C141:C144"/>
+    <mergeCell ref="B145:B148"/>
+    <mergeCell ref="C145:C148"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="B223:B225"/>
+    <mergeCell ref="C223:C225"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="B161:B164"/>
+    <mergeCell ref="C161:C164"/>
+    <mergeCell ref="B167:B169"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:Y225">
     <cfRule type="colorScale" priority="5">
@@ -67416,17 +67389,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3:AS225">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV3:BO225">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.70866141732283472" right="0.51181102362204722" top="0.51181102362204722" bottom="0.51181102362204722" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="43" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0.51181102362204722" top="0.47244094488188981" bottom="0.51181102362204722" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="42" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
